--- a/Probabili_Formazioni_Serie_A_Squadre.xlsx
+++ b/Probabili_Formazioni_Serie_A_Squadre.xlsx
@@ -574,35 +574,34 @@
       <c r="C5" s="5" t="inlineStr">
         <is>
           <t>• Carnesecchi (95%)
-• Zappacosta (60%)
+• Zappacosta (95%)
+• Kossounou (95%)
 • Scalvini (95%)
 • Kolasinac (55%)
-• Bernasconi (95%)
 • Samardzic (51%)
-• Gaetano (55%)
+• Gaetano (95%)
 • Ederson D.S. (95%)
-• Zalewski (95%)
-• Scamacca (51%)
-• Raspadori (95%)</t>
+• De Ketelaere (95%)
+• Scamacca (55%)
+• Raspadori (60%)</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>• Zappacosta (60%) - Bellanova (40%)
-• Kolasinac (55%) - Kristensen T. (45%)
+          <t>• Kolasinac (55%) - Bernasconi (45%)
 • Samardzic (51%) - Pasalic (49%)
-• Gaetano (55%) - De Roon (45%)
-• Scamacca (51%) - Krstovic (49%)</t>
+• Scamacca (55%) - Krstovic (45%)
+• Raspadori (60%) - Elmas (40%)</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Bellanova (40%), Krstovic (49%), De Roon (45%), Pasalic (49%), Kossounou (10%), Kristensen T. (45%)</t>
+          <t>Bernasconi (45%), Pasalic (49%), Elmas (40%), Krstovic (45%), Pompei (5%), Sportiello (5%), Bellanova (5%), Kessiè (5%), Rowe (5%), Zalewski (5%)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Ahanor, Hien, Sulemana K., De Ketelaere, Konè I.</t>
+          <t>Hien, Sulemana K., Kristensen T.</t>
         </is>
       </c>
     </row>
@@ -620,32 +619,35 @@
       <c r="C6" s="7" t="inlineStr">
         <is>
           <t>• Skorupski (95%)
-• Zortea (95%)
+• Zortea (51%)
+• Theate (51%)
 • Heggem (95%)
-• Vitik (95%)
-• Miranda J. (95%)
+• Miranda J. (51%)
+• Odgaard (95%)
+• Pobega (51%)
+• Ferguson (95%)
 • Bernardeschi (95%)
-• Pobega (60%)
-• Ferguson (95%)
-• Orsolini (95%)
-• Dovbyk (95%)
-• Rowe (60%)</t>
+• Piccoli (55%)
+• Cambiaghi (95%)</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>• Pobega (60%) - Moro N. (40%)
-• Rowe (60%) - Cambiaghi (40%)</t>
+          <t>• Zortea (51%) - Holm (49%)
+• Theate (51%) - Helland (49%)
+• Miranda J. (51%) - Alhassane (49%)
+• Pobega (51%) - Moro N. (49%)
+• Piccoli (55%) - Dovbyk (45%)</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Cambiaghi (40%), Moro N. (40%), Castro S. (20%), Pisilli (20%)</t>
+          <t>Dovbyk (45%), Moro N. (49%), Holm (49%), Helland (49%), Alhassane (49%), Pessina Mas. (5%), Happonen (5%), Casale (5%), De Silvestri (5%), Vitik (5%), Amondarain (5%), Mbangula (5%), Enem (5%)</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Casale</t>
+          <t>El Azzouzi O., Orsolini</t>
         </is>
       </c>
     </row>
@@ -708,31 +710,34 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>• Butez (95%)
-• Couto (51%)
-• Ramon (55%)
-• Chalobah T. (95%)
-• Valle (51%)
-• Perrone (70%)
-• Da Cunha (95%)
-• Diao (60%)
+          <t>• Butez (55%)
+• Couto (60%)
+• Ramon (60%)
+• Chalobah T. (60%)
+• Valle (60%)
+• Perrone (95%)
+• Da Cunha (51%)
+• Diao (55%)
 • Paz N. (95%)
 • Baturina (95%)
-• Douvikas (95%)</t>
+• Douvikas (60%)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>• Couto (51%) - Smolcic I. (49%)
-• Ramon (55%) - Kempf (45%)
-• Valle (51%) - Kaiki (49%)
-• Perrone (70%) - Milla (30%)
-• Diao (60%) - Rodriguez Je. (40%)</t>
+          <t>• Butez (55%) - Sanchez Ro. (45%)
+• Couto (60%) - Smolcic I. (40%)
+• Ramon (60%) - Kempf (40%)
+• Chalobah T. (60%) - Kempf (40%)
+• Valle (60%) - Kaiki (40%)
+• Da Cunha (51%) - Milla (49%)
+• Diao (55%) - Rodriguez Je. (45%)
+• Douvikas (60%) - Kean (40%)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Rodriguez Je. (40%), Kaiki (49%), Milla (30%), Smolcic I. (49%), Kempf (45%)</t>
+          <t>Smolcic I. (40%), Kempf (40%), Kaiki (40%), Rodriguez Je. (45%), Sanchez Ro. (45%), Milla (49%), Kean (40%), Vigorito (5%), Goldaniga (5%), Kambwala (5%), Caqueret (5%), Lahdo (5%), Liberali (5%), Ricci S. (5%)</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -757,28 +762,29 @@
           <t>• De Gea (95%)
 • Jimenez A. (51%)
 • Dragusin (95%)
-• Viery (55%)
-• Valdepenas (95%)
+• Pongracic (51%)
+• Valdepenas (55%)
+• Ndour (95%)
 • Oulai (55%)
-• Fagioli (95%)
-• Ndour (55%)
 • Atta (95%)
-• Gudmundsson A. (51%)
-• Kean (95%)</t>
+• Mastantuono (95%)
+• Goncalves P. (51%)
+• Pellegrino M. (60%)</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>• Jimenez A. (51%) - Joao Mario (49%)
-• Viery (55%) - Ranieri L. (45%)
-• Oulai (55%) - Ndour (55%)
-• Ndour (55%) - Mandragora (45%)
-• Gudmundsson A. (51%) - Mastantuono (49%)</t>
+          <t>• Jimenez A. (51%) - Dodò (49%)
+• Pongracic (51%) - Viery (49%)
+• Valdepenas (55%) - Joao Mario (45%)
+• Oulai (55%) - Fagioli (45%)
+• Goncalves P. (51%) - Njie (49%)
+• Pellegrino M. (60%) - Beto (40%)</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Joao Mario (49%), Mastantuono (49%), Mandragora (45%), Ranieri L. (45%), Dodò (5%), Pellegrino M. (5%)</t>
+          <t>Viery (49%), Dodò (49%), Joao Mario (45%), Fagioli (45%), Njie (49%), Beto (40%), Christensen O. (5%), Lezzerini (5%), Ranieri L. (5%), Brescianini (5%), Gnonto (5%)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -795,42 +801,42 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>4-3-3</t>
+          <t>4-2-3-1</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>• Palmisani (60%)
-• Oyono A. (95%)
-• Akpoguma (95%)
+          <t>• Palmisani (95%)
+• Oyono A. (51%)
+• Calvani (60%)
 • Monterisi (60%)
-• Terzic (60%)
-• Masini (55%)
-• Grillitsch (70%)
-• Schmid (95%)
-• Ghedjemis (95%)
-• Raimondo (95%)
-• Kvernadze (55%)</t>
+• Bracaglia (60%)
+• Calò (95%)
+• Masini (95%)
+• Kvernadze (95%)
+• Schmid (51%)
+• Ghedjemis (51%)
+• Raimondo (95%)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>• Palmisani (60%) - Desplanches (40%)
-• Monterisi (60%) - Calvani (40%)
-• Terzic (60%) - Bracaglia (40%)
-• Masini (55%) - El Azzouzi A. (45%)
-• Grillitsch (70%) - Calò (30%)
-• Kvernadze (55%) - Zerbin (45%)</t>
+          <t>• Oyono A. (51%) - Tchato (49%)
+• Calvani (60%) - Akpoguma (40%)
+• Monterisi (60%) - Akpoguma (40%)
+• Bracaglia (60%) - Terzic (40%)
+• Schmid (51%) - Grillitsch (49%)
+• Ghedjemis (51%) - Fini (49%)</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Desplanches (40%), Gelli J. (10%), Calvani (40%), Hasa (20%), Fini (30%), Gelli F. (45%), Calò (30%), Bracaglia (40%), El Azzouzi A. (45%), Zerbin (45%)</t>
+          <t>Akpoguma (40%), Terzic (40%), Tchato (49%), Grillitsch (49%), Fini (49%), Desplanches (5%), Pisseri (5%), Amey (5%), Cittadini (5%), Omar Fayed (5%), Cichella (5%), El Azzouzi A. (5%), Hasa (5%), Zerbin (5%), Birligea (5%), Bobcek (5%)</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>Ekhator</t>
+          <t>Gelli F., Lolic, Kone B., Koutsoupias</t>
         </is>
       </c>
     </row>
@@ -842,7 +848,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3-4-2-1</t>
+          <t>3-5-2</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -851,29 +857,28 @@
 • Marcandalli (95%)
 • Ostigard (95%)
 • Vasquez (95%)
-• Norton-Cuffy (95%)
+• Ellertsson (95%)
+• Sow (95%)
 • Frendrup (95%)
-• Sow (55%)
-• Mitaj (55%)
 • Baldanzi (95%)
-• Vitinha O. (95%)
+• Mitaj (95%)
+• Vitinha O. (60%)
 • Colombo (95%)</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>• Sow (55%) - Ellertsson (49%)
-• Mitaj (55%) - Ellertsson (49%)</t>
+          <t>• Vitinha O. (60%) - Meichtry (40%)</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Ellertsson (49%), Giovane (10%)</t>
+          <t>Meichtry (40%), Sommariva (5%), Stolz (5%), Otoa (5%), Puczka (5%), Sabelli (5%), Amorim (5%), El Shaarawy (5%), Messias (5%), Traorè Hj. (5%), Havel (5%), Osmajic (5%), Robinho Junior (5%)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Venturino</t>
+          <t>Venturino, Drameh</t>
         </is>
       </c>
     </row>
@@ -891,35 +896,34 @@
       <c r="C12" s="7" t="inlineStr">
         <is>
           <t>• Martinez Jo. (95%)
+• Stones (51%)
 • Akanji (95%)
-• Stones (51%)
 • Bastoni (95%)
-• Diouf (70%)
+• Diouf (51%)
 • Barella (95%)
 • Calhanoglu (95%)
-• Zielinski (55%)
+• Jones C. (51%)
 • Dimarco (95%)
-• Martinez L. (51%)
-• Esposito F.P. (60%)</t>
+• Martinez L. (95%)
+• Esposito F.P. (51%)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
           <t>• Stones (51%) - Bisseck (49%)
-• Diouf (70%) - Spence (30%)
-• Zielinski (55%) - Sucic P. (45%)
-• Martinez L. (51%) - Bonny (49%)
-• Esposito F.P. (60%) - Thuram (40%)</t>
+• Diouf (51%) - Luis Henrique (49%)
+• Jones C. (51%) - Zielinski (49%)
+• Esposito F.P. (51%) - Thuram (49%)</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Sucic P. (45%), Bisseck (49%), Spence (30%), Thuram (40%), Bonny (49%)</t>
+          <t>Sucic P. (10%), Luis Henrique (49%), Bisseck (49%), Zielinski (49%), Thuram (49%), Di Gennaro (5%), Provedel (5%), Carlos Augusto (5%), Pavard (5%), Mkhitaryan (5%), Stankovic A. (5%), Bonny (5%)</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>Mkhitaryan (Squalificato)</t>
+          <t>Spence</t>
         </is>
       </c>
     </row>
@@ -1113,33 +1117,34 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>• Thiam (95%)
+          <t>• Tornqvist (95%)
 • Kouadio (95%)
-• Delli Carri (95%)
+• Ziolkowski (95%)
 • Carboni A. (95%)
 • Birindelli (95%)
-• Akinsanmiro (95%)
-• Colombo L. (95%)
+• Folorunsho (55%)
+• Akinsanmiro (55%)
 • Mangas (95%)
-• Colpani (60%)
-• Mota (95%)
-• Cutrone (60%)</t>
+• Colpani (95%)
+• Mota (55%)
+• Cutrone (95%)</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>• Colpani (60%) - Ciurria (40%)
-• Cutrone (60%) - Varela G. (40%)</t>
+          <t>• Folorunsho (55%) - Foe Ondoa (45%)
+• Akinsanmiro (55%) - Mout (45%)
+• Mota (55%) - Forson O. (45%)</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Ciurria (40%), Varela G. (40%)</t>
+          <t>Mout (45%), Foe Ondoa (45%), Varela G., Forson O. (45%), Strajnar (5%), Thiam (5%), Antov (5%), Bakoune (5%), Goglichidze (5%), Lucchesi (5%), Maye (5%), Colombo L. (5%), Tourè I. (5%), Ngonge (5%), Robinson J. (5%), Zeballos (5%)</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Pessina</t>
+          <t>Pessina, Ciurria</t>
         </is>
       </c>
     </row>
@@ -1156,34 +1161,34 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>• Meret (55%)
+          <t>• Meret (95%)
 • Di Lorenzo (95%)
 • Rrahmani (95%)
-• Marin R. (51%)
-• Spinazzola (95%)
-• De Bruyne (70%)
+• Marin R. (95%)
+• Spinazzola (51%)
+• Zambo Anguissa (95%)
 • Lobotka (95%)
-• Mctominay (95%)
-• Politano (95%)
+• De Bruyne (95%)
+• Politano (51%)
 • Hojlund (95%)
-• Santos A. (95%)</t>
+• Santos A. (51%)</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>• Meret (55%) - Milinkovic-Savic V. (45%)
-• Marin R. (51%) - Olivera (49%)
-• De Bruyne (70%) - Zambo Anguissa (30%)</t>
+          <t>• Spinazzola (51%) - Olivera (49%)
+• Politano (51%) - Vergara (49%)
+• Santos A. (51%) - Lang (49%)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Olivera (49%), Milinkovic-Savic V. (45%), Zambo Anguissa (30%)</t>
+          <t>Lang (49%), Olivera (49%), Vergara (49%), Contini (5%), Milinkovic-Savic V. (5%), Badiashile (5%), Beukema (5%), Favasuli (5%), Gilmour (5%), Lucca (5%), Neres (5%)</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>Buongiorno, Beukema, Marianucci, Neres</t>
+          <t>Buongiorno, Marianucci, Mctominay, Giovane</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1200,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>4-3-3</t>
+          <t>4-3-2-1</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1203,29 +1208,32 @@
           <t>• Corvi (95%)
 • Delprato (95%)
 • Troilo (95%)
-• Circati (95%)
+• Diego Carlos (51%)
 • Valeri (95%)
 • Bernabè (95%)
+• Ordonez C. (55%)
 • Keita M. (95%)
-• Sorensen O. (55%)
-• Frigan (95%)
-• Romero D. (95%)
-• Tourè E. (95%)</t>
+• Britschgi (95%)
+• Tourè E. (60%)
+• Romero D. (60%)</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>• Sorensen O. (55%) - Ordonez C. (45%)</t>
+          <t>• Diego Carlos (51%) - Drobnic (49%)
+• Ordonez C. (55%) - Fabbian (45%)
+• Tourè E. (60%) - Elphege (40%)
+• Romero D. (60%) - Lontani (40%)</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Ordonez C. (45%), Pellegrino M. (10%), Daffara (5%), Suzuki (5%)</t>
+          <t>Fabbian (45%), Drobnic (49%), Lontani (40%), Elphege (40%), Daffara (5%), Ghidotti (5%), Carboni F. (5%), Ndiaye (5%), Valenti (5%), Almqvist (5%), Cremaschi (5%), Diallo O. (5%), Konaté A. (5%), De Martis (5%), Frigan (5%)</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Cremaschi, Britschgi (Squalificato)</t>
+          <t>Nicolussi Caviglia</t>
         </is>
       </c>
     </row>
@@ -1243,34 +1251,31 @@
       <c r="C20" s="7" t="inlineStr">
         <is>
           <t>• Svilar (95%)
+• Ghilardi (55%)
 • Mancini (95%)
-• N'Dicka (95%)
-• Koulierakis (60%)
-• Molina N. (95%)
+• Hermoso (95%)
+• Molina N. (51%)
 • Konè M. (95%)
 • Cristante (95%)
 • Wesley (95%)
-• Soulè (51%)
 • Dybala (95%)
+• Mora (51%)
 • Malen (95%)</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>• Koulierakis (60%) - Hermoso (40%)
-• Soulè (51%) - Pellegrini Lo. (49%)</t>
+          <t>• Ghilardi (55%) - N'Dicka (45%)
+• Molina N. (51%) - Lulli (49%)
+• Mora (51%) - Soulè (49%)</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Hermoso (40%), Pellegrini Lo. (49%)</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Vaz</t>
-        </is>
-      </c>
+          <t>N'Dicka (45%), Lulli (49%), Soulè (49%), De Marzi (5%), Gollini (5%), Balerdi (5%), Koulierakis (5%), Rensch (5%), De Roon (5%), Pellegrini Lo. (5%), Pisilli (5%), Castro S. (5%)</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr"/>
     </row>
     <row r="21" ht="165" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -1280,41 +1285,41 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>4-2-3-1</t>
+          <t>4-3-3</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
           <t>• Muric (95%)
-• Missori (95%)
-• Walukiewicz (95%)
+• Van Der Brempt (55%)
 • Idzes (95%)
-• Obrador (51%)
-• Lipani (60%)
+• Leysen F. (95%)
+• Doig (51%)
+• Adzic (51%)
 • Matic (95%)
-• Volpato (55%)
-• Thorstvedt (51%)
-• Laurientè (95%)
-• Pinamonti (60%)</t>
+• Bakola (95%)
+• Berardi (60%)
+• Bowie (51%)
+• Laurientè (95%)</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>• Obrador (51%) - Doig (49%)
-• Lipani (60%) - Bakola (40%)
-• Volpato (55%) - Dominguez B. (45%)
-• Thorstvedt (51%) - Adzic (49%)
-• Pinamonti (60%) - Bowie (40%)</t>
+          <t>• Van Der Brempt (55%) - Cinquegrano (45%)
+• Doig (51%) - Obrador (49%)
+• Adzic (51%) - Thorstvedt (49%)
+• Berardi (60%) - Volpato (40%)
+• Bowie (51%) - Esposito Se. (49%)</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Turati (49%), Bowie (40%), Bakola (40%), Doig (49%), Berardi (5%), Adzic (49%), Dominguez B. (45%)</t>
+          <t>Obrador (49%), Thorstvedt (49%), Esposito Se. (49%), Volpato (40%), Cinquegrano (45%), Satalino (5%), Turati (5%), Caleta-Car (5%), Odenthal (5%), Dominguez B. (5%), Lipani (5%), Sulemana I. (5%)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Boloca, Candè, Pieragnolo</t>
+          <t>Candè, Pieragnolo, Russo A., Walukiewicz, Konè I., Boloca</t>
         </is>
       </c>
     </row>
@@ -1331,34 +1336,35 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>• Paleari (95%)
-• Ismajli (95%)
+          <t>• Perri (70%)
+• Comuzzo (95%)
 • Coco (95%)
-• Comuzzo (55%)
-• Pedersen (95%)
+• Comert (60%)
+• Fortini (51%)
 • Fitz-Jim (95%)
-• Casadei (51%)
+• Mandragora (51%)
 • Cacciamani (95%)
-• Oristanio (55%)
 • Vlasic (95%)
+• Adams C. (95%)
 • Simeone (95%)</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>• Comuzzo (55%) - Comert (45%)
-• Casadei (51%) - Gineitis (49%)
-• Oristanio (55%) - Adams C. (45%)</t>
+          <t>• Perri (70%) - Mascardi (30%)
+• Comert (60%) - Ismajli (40%)
+• Fortini (51%) - Belghali (49%)
+• Mandragora (51%) - Gineitis (49%)</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Gineitis (49%), Comert (45%), Adams C. (45%)</t>
+          <t>Mascardi (30%), Ismajli (40%), Belghali (49%), Gineitis (49%), Paleari (5%), Siviero (5%), Patterson (5%), Aboukhlal (5%), Anjorin (5%), Braganca (5%), Ilkhan (5%), Oristanio (5%), Kulenovic (5%), Zapata D. (5%)</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Gimenez</t>
+          <t>Casadei, Biraghi</t>
         </is>
       </c>
     </row>
@@ -1419,35 +1425,34 @@
       <c r="C24" s="7" t="inlineStr">
         <is>
           <t>• Stankovic F. (95%)
-• Schingtienne (55%)
+• Schingtienne (95%)
 • Bella-Kotchap (95%)
-• Moreno M. (70%)
-• Correia T. (60%)
-• Basic (95%)
+• Halhal (55%)
+• Hainaut (60%)
+• Basic (55%)
 • Busio (95%)
-• Sohm (95%)
+• Perez K. (55%)
 • Haps (95%)
-• Yeboah J. (70%)
-• Adams A. (70%)</t>
+• Yeboah J. (95%)
+• Adams A. (95%)</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>• Schingtienne (55%) - Halhal (45%)
-• Moreno M. (70%) - Franjic (30%)
-• Correia T. (60%) - Hainaut (40%)
-• Yeboah J. (70%) - Rrahmani Al. (30%)
-• Adams A. (70%) - Rrahmani Al. (30%)</t>
+          <t>• Halhal (55%) - Juan Jesus (45%)
+• Hainaut (60%) - Mazzocchi (40%)
+• Basic (55%) - Sohm (45%)
+• Perez K. (55%) - Sohm (45%)</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Halhal (45%), Franjic (30%), Hainaut (40%), Rrahmani Al. (30%), Perez K. (5%)</t>
+          <t>Juan Jesus (45%), Sohm (45%), Mazzocchi (40%), Grandi (5%), Montipò (5%), Pozzi (5%), Correia T. (5%), Gomes (5%), Sagrado (5%), Dagasso (5%), Fernandez T. (5%), Helgason (5%), Lauberbach (5%), Lisman (5%), Rrahmani Al. (5%)</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>Sverko, Adorante</t>
+          <t>Sverko, Adorante, Moreno M., Duncan, Franjic</t>
         </is>
       </c>
     </row>
